--- a/data/trans_camb/P14B23-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P14B23-Estudios-trans_camb.xlsx
@@ -513,7 +513,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con enfermedades crónicas discapacitantes de salud mental (trastornos depresivos o ansiedad)</t>
+          <t>Población cuya depresión o ansiedad le limita</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 0,67</t>
+          <t>-3,13; 0,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,07</t>
+          <t>0,92; 6,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 2,08</t>
+          <t>-3,97; 2,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 1,92</t>
+          <t>-3,37; 2,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 0,94</t>
+          <t>-3,17; 0,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 2,9</t>
+          <t>-0,83; 2,89</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-57,17; 20,48</t>
+          <t>-54,27; 22,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,2; 161,92</t>
+          <t>15,8; 170,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-23,94; 16,57</t>
+          <t>-26,23; 17,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,57; 16,06</t>
+          <t>-21,69; 17,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-28,22; 10,33</t>
+          <t>-29,26; 8,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 32,35</t>
+          <t>-7,71; 31,38</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 0,82</t>
+          <t>-1,05; 0,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 2,01</t>
+          <t>-0,29; 2,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 1,36</t>
+          <t>-1,53; 1,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 2,93</t>
+          <t>-0,73; 2,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,89</t>
+          <t>-0,9; 0,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 2,05</t>
+          <t>0,01; 2,08</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-40,27; 57,49</t>
+          <t>-42,15; 62,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 131,29</t>
+          <t>-13,11; 141,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-27,86; 30,03</t>
+          <t>-25,51; 35,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,63; 65,13</t>
+          <t>-11,58; 67,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,5; 31,19</t>
+          <t>-23,03; 27,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 67,6</t>
+          <t>0,54; 69,25</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,71</t>
+          <t>-1,78; 0,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,4</t>
+          <t>0,75; 4,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 1,36</t>
+          <t>-2,21; 1,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 3,95</t>
+          <t>0,05; 4,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,79</t>
+          <t>-1,38; 0,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,64</t>
+          <t>0,95; 3,52</t>
         </is>
       </c>
     </row>
@@ -1024,27 +1024,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,62; —</t>
+          <t>-36,93; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-78,91; 157,88</t>
+          <t>-73,16; 206,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 391,35</t>
+          <t>-3,43; 561,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-69,08; 134,91</t>
+          <t>-69,86; 131,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,62; 589,74</t>
+          <t>32,72; 548,8</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,23</t>
+          <t>-1,25; 0,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 2,15</t>
+          <t>0,04; 2,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,61; -0,14</t>
+          <t>-2,56; -0,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 0,54</t>
+          <t>-2,33; 0,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,73; -0,18</t>
+          <t>-1,67; -0,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,04</t>
+          <t>-0,76; 1,09</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-42,77; 12,03</t>
+          <t>-42,03; 12,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,73; 100,18</t>
+          <t>1,04; 94,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-30,68; -1,96</t>
+          <t>-29,99; -1,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-26,46; 7,01</t>
+          <t>-27,6; 8,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,77; -3,37</t>
+          <t>-28,87; -1,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-12,36; 20,51</t>
+          <t>-12,99; 22,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P14B23-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P14B23-Estudios-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,33</t>
+          <t>2,75</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,75</t>
+          <t>-0,6</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>0,87</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 0,74</t>
+          <t>-3,17; 0,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 6,14</t>
+          <t>0,18; 5,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 2,07</t>
+          <t>-3,82; 1,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 2,16</t>
+          <t>-3,06; 2,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 0,79</t>
+          <t>-2,99; 0,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 2,89</t>
+          <t>-1,08; 2,76</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-5,33%</t>
+          <t>-4,26%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-54,27; 22,99</t>
+          <t>-54,96; 20,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,8; 170,11</t>
+          <t>-0,64; 133,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-26,23; 17,28</t>
+          <t>-25,06; 14,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,69; 17,48</t>
+          <t>-20,13; 16,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,26; 8,74</t>
+          <t>-27,64; 8,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 31,38</t>
+          <t>-10,26; 30,43</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>1,24</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>2,2</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>1,78</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 0,88</t>
+          <t>-1,06; 0,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 2,1</t>
+          <t>0,29; 2,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 1,46</t>
+          <t>-1,68; 1,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 2,89</t>
+          <t>0,63; 3,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,8</t>
+          <t>-0,89; 0,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,01; 2,08</t>
+          <t>0,88; 2,69</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>52,27%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-42,15; 62,13</t>
+          <t>-43,14; 55,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,11; 141,86</t>
+          <t>5,17; 158,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-25,51; 35,21</t>
+          <t>-27,97; 30,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 67,72</t>
+          <t>10,52; 82,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,03; 27,16</t>
+          <t>-22,98; 30,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 69,25</t>
+          <t>21,16; 87,09</t>
         </is>
       </c>
     </row>
@@ -910,27 +910,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>2,56</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-0,26</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2,32</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>-0,15</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>2,46</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,26</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,14</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,15</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,32</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,69</t>
+          <t>-1,47; 0,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 4,38</t>
+          <t>0,89; 4,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 1,57</t>
+          <t>-2,26; 1,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 4,09</t>
+          <t>0,37; 4,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 0,77</t>
+          <t>-1,29; 0,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,52</t>
+          <t>0,96; 3,71</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>410,35%</t>
+          <t>425,68%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>114,89%</t>
+          <t>124,49%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>190,93%</t>
+          <t>202,34%</t>
         </is>
       </c>
     </row>
@@ -1024,27 +1024,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-36,93; —</t>
+          <t>-11,87; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-73,16; 206,71</t>
+          <t>-75,92; 154,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 561,5</t>
+          <t>0,9; 465,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-69,86; 131,19</t>
+          <t>-68,49; 150,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,72; 548,8</t>
+          <t>37,15; 593,62</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>1,35</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,68</t>
+          <t>-0,0</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>0,68</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,22</t>
+          <t>-1,3; 0,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,04</t>
+          <t>0,47; 2,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,56; -0,09</t>
+          <t>-2,61; 0,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 0,62</t>
+          <t>-1,25; 1,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,67; -0,1</t>
+          <t>-1,6; -0,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,09</t>
+          <t>-0,02; 1,44</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-8,52%</t>
+          <t>-0,03%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-42,03; 12,97</t>
+          <t>-44,11; 12,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,04; 94,37</t>
+          <t>15,29; 111,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-29,99; -1,49</t>
+          <t>-30,08; -0,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,6; 8,14</t>
+          <t>-14,23; 16,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-28,87; -1,72</t>
+          <t>-27,81; -3,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 22,53</t>
+          <t>-0,6; 28,71</t>
         </is>
       </c>
     </row>
